--- a/practice/answers/s1_q21.xlsx
+++ b/practice/answers/s1_q21.xlsx
@@ -565,7 +565,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Kestrel</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
@@ -587,7 +587,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Meadowvale</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
@@ -609,7 +609,7 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Creek</t>
+          <t>Nightjar</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">

--- a/practice/answers/s1_q21.xlsx
+++ b/practice/answers/s1_q21.xlsx
@@ -16,10 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -68,7 +66,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +76,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F6EFD9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004A7C59"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,31 +96,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -487,28 +496,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Three scenarios from one formula</t>
+          <t>Squaring with ^, and what PEMDAS does with it</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fields down, seeding rates across. The acres reference locks its column and the rate reference locks its row, so one formula fills the whole grid.</t>
+          <t>A square bin's floor is the side length squared. The exponent runs before any multiplication unless brackets say otherwise.</t>
         </is>
       </c>
     </row>
@@ -516,181 +525,215 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Seed price ($/lb)</t>
+          <t>Grain density (t/m3)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1.85</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1"/>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Acres</t>
+          <t>Bin</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Side (m)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Depth (m)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>Floor area (m2)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Volume (m3)</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Capacity (t)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="C7" s="7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>3.5</v>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Bin 1</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D7" s="4">
+        <f>B7^2</f>
+        <v/>
+      </c>
+      <c r="E7" s="10">
+        <f>D7*C7</f>
+        <v/>
+      </c>
+      <c r="F7" s="11">
+        <f>ROUND(E7*$B$4,0)</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Kestrel</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="C8" s="10">
-        <f>$B8*C$7</f>
-        <v/>
-      </c>
-      <c r="D8" s="10">
-        <f>$B8*D$7</f>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Bin 2</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D8" s="4">
+        <f>B8^2</f>
         <v/>
       </c>
       <c r="E8" s="10">
-        <f>$B8*E$7</f>
+        <f>D8*C8</f>
+        <v/>
+      </c>
+      <c r="F8" s="11">
+        <f>ROUND(E8*$B$4,0)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Meadowvale</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>240</v>
-      </c>
-      <c r="C9" s="10">
-        <f>$B9*C$7</f>
-        <v/>
-      </c>
-      <c r="D9" s="10">
-        <f>$B9*D$7</f>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Bin 3</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="4">
+        <f>B9^2</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>$B9*E$7</f>
+        <f>D9*C9</f>
+        <v/>
+      </c>
+      <c r="F9" s="11">
+        <f>ROUND(E9*$B$4,0)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Nightjar</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>95</v>
-      </c>
-      <c r="C10" s="10">
-        <f>$B10*C$7</f>
-        <v/>
-      </c>
-      <c r="D10" s="10">
-        <f>$B10*D$7</f>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Bin 4</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D10" s="4">
+        <f>B10^2</f>
         <v/>
       </c>
       <c r="E10" s="10">
-        <f>$B10*E$7</f>
+        <f>D10*C10</f>
+        <v/>
+      </c>
+      <c r="F10" s="11">
+        <f>ROUND(E10*$B$4,0)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Total lb</t>
-        </is>
-      </c>
-      <c r="C11" s="11">
-        <f>SUM(C8:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="11">
-        <f>SUM(D8:D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="11">
-        <f>SUM(E8:E10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Seed cost</t>
-        </is>
-      </c>
-      <c r="C12" s="4">
-        <f>C11*$B$4</f>
-        <v/>
-      </c>
-      <c r="D12" s="4">
-        <f>D11*$B$4</f>
-        <v/>
-      </c>
-      <c r="E12" s="4">
-        <f>E11*$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1"/>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>The one formula</t>
-        </is>
-      </c>
-      <c r="C14" s="12">
-        <f>_xlfn.FORMULATEXT(C8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1"/>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>1,092.0 / 1,319.5 / 1,592.5 lb, costing $2,020.20 / $2,441.08 / $2,946.13. One formula covers all nine cells, so changing an acre figure or a rate updates everything at once.</t>
-        </is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E11" s="12">
+        <f>SUM(E7:E10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="13">
+        <f>SUM(F7:F10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1"/>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>The formula in D7</t>
+        </is>
+      </c>
+      <c r="D13" s="14">
+        <f>_xlfn.FORMULATEXT(D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1"/>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3">
+        <f>4*3^2</f>
+        <v/>
+      </c>
+      <c r="C15" s="11">
+        <f>4*3^2</f>
+        <v/>
+      </c>
+      <c r="E15" s="14">
+        <f>_xlfn.FORMULATEXT(C15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3">
+        <f>(4*3)^2</f>
+        <v/>
+      </c>
+      <c r="C16" s="11">
+        <f>(4*3)^2</f>
+        <v/>
+      </c>
+      <c r="E16" s="14">
+        <f>_xlfn.FORMULATEXT(C16)</f>
+        <v/>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1"/>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>36 and 144. Exponents run before multiplication, so the first squares the 3 and then multiplies by 4. Doubling a side instead of squaring it gives a distance, not an area -- 22.5 m against 126.56 m2 for Bin 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q21.xlsx
+++ b/practice/answers/s1_q21.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,45 +29,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -75,12 +41,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,41 +77,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -496,244 +465,277 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Squaring with ^, and what PEMDAS does with it</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>A square bin's floor is the side length squared. The exponent runs before any multiplication unless brackets say otherwise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Grain density (t/m3)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
+          <t>Bin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Side (m)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Depth (m)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Floor area (m²)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Volume (m³)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Capacity (t)</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Tonnes per m³</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="n">
         <v>0.75</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1"/>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Bin</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Side (m)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Depth (m)</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Floor area (m2)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Volume (m3)</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Capacity (t)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Bin 1</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B2" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C2" s="7" t="n">
         <v>4.2</v>
       </c>
-      <c r="D7" s="4">
-        <f>B7^2</f>
-        <v/>
-      </c>
-      <c r="E7" s="10">
-        <f>D7*C7</f>
-        <v/>
-      </c>
-      <c r="F7" s="11">
-        <f>ROUND(E7*$B$4,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="D2" s="8">
+        <f>B2^2</f>
+        <v/>
+      </c>
+      <c r="E2" s="9">
+        <f>D2*C2</f>
+        <v/>
+      </c>
+      <c r="F2" s="10">
+        <f>ROUND(E2*$H$1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Bin 2</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B3" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C3" s="7" t="n">
         <v>3.8</v>
       </c>
-      <c r="D8" s="4">
-        <f>B8^2</f>
-        <v/>
-      </c>
-      <c r="E8" s="10">
-        <f>D8*C8</f>
-        <v/>
-      </c>
-      <c r="F8" s="11">
-        <f>ROUND(E8*$B$4,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="D3" s="8">
+        <f>B3^2</f>
+        <v/>
+      </c>
+      <c r="E3" s="9">
+        <f>D3*C3</f>
+        <v/>
+      </c>
+      <c r="F3" s="10">
+        <f>ROUND(E3*$H$1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Bin 3</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B4" s="6" t="n">
         <v>11.25</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="4">
-        <f>B9^2</f>
-        <v/>
-      </c>
-      <c r="E9" s="10">
-        <f>D9*C9</f>
-        <v/>
-      </c>
-      <c r="F9" s="11">
-        <f>ROUND(E9*$B$4,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="D4" s="8">
+        <f>B4^2</f>
+        <v/>
+      </c>
+      <c r="E4" s="9">
+        <f>D4*C4</f>
+        <v/>
+      </c>
+      <c r="F4" s="10">
+        <f>ROUND(E4*$H$1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Bin 4</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B5" s="6" t="n">
         <v>6.4</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C5" s="7" t="n">
         <v>4.5</v>
       </c>
-      <c r="D10" s="4">
-        <f>B10^2</f>
-        <v/>
-      </c>
-      <c r="E10" s="10">
-        <f>D10*C10</f>
-        <v/>
-      </c>
-      <c r="F10" s="11">
-        <f>ROUND(E10*$B$4,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="D5" s="8">
+        <f>B5^2</f>
+        <v/>
+      </c>
+      <c r="E5" s="9">
+        <f>D5*C5</f>
+        <v/>
+      </c>
+      <c r="F5" s="10">
+        <f>ROUND(E5*$H$1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E11" s="12">
-        <f>SUM(E7:E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="13">
-        <f>SUM(F7:F10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1"/>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>The formula in D7</t>
-        </is>
-      </c>
-      <c r="D13" s="14">
-        <f>_xlfn.FORMULATEXT(D7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1"/>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="3">
+      <c r="E6" s="9">
+        <f>SUM(E2:E5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11">
+        <f>4*3^2 gives</f>
+        <v/>
+      </c>
+      <c r="B8" s="11">
         <f>4*3^2</f>
         <v/>
       </c>
-      <c r="C15" s="11">
-        <f>4*3^2</f>
-        <v/>
-      </c>
-      <c r="E15" s="14">
-        <f>_xlfn.FORMULATEXT(C15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="3">
+    </row>
+    <row r="9">
+      <c r="A9" s="11">
+        <f>(4*3)^2 gives</f>
+        <v/>
+      </c>
+      <c r="B9" s="11">
         <f>(4*3)^2</f>
         <v/>
       </c>
-      <c r="C16" s="11">
-        <f>(4*3)^2</f>
-        <v/>
-      </c>
-      <c r="E16" s="14">
-        <f>_xlfn.FORMULATEXT(C16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1"/>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>36 and 144. Exponents run before multiplication, so the first squares the 3 and then multiplies by 4. Doubling a side instead of squaring it gives a distance, not an area -- 22.5 m against 126.56 m2 for Bin 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>The two cells return 36 and 144. Exponents are evaluated before multiplication, so =4*3^2 squares the 3 and then multiplies by 4; the brackets in =(4*3)^2 force the multiplication first, and 12 squared is 144.</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>They doubled the side length instead of squaring it -- 11.25*2 is 22.5 m, a distance, not an area. Squaring gives 126.56 m².</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n"/>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
+      <c r="H15" s="14" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A14:H15"/>
+    <mergeCell ref="A11:H12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q21.xlsx
+++ b/practice/answers/s1_q21.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -32,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,16 +54,6 @@
         <fgColor rgb="00CFE2F3"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -77,26 +67,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -465,278 +442,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bin</t>
+          <t>Crop</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Side (m)</t>
+          <t>Yield (bu/ac)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Depth (m)</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Floor area (m²)</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Volume (m³)</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Capacity (t)</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Tonnes per m³</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="n">
-        <v>0.75</v>
+          <t>Price ($/bu)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cost ($/ac)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue ($/ac) (a)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Profit ($/ac) (b)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Margin (c)</t>
+        </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bin 1</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="C2" s="7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D2" s="8">
-        <f>B2^2</f>
-        <v/>
-      </c>
-      <c r="E2" s="9">
-        <f>D2*C2</f>
-        <v/>
-      </c>
-      <c r="F2" s="10">
-        <f>ROUND(E2*$H$1,0)</f>
+          <t>Canola</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>415</v>
+      </c>
+      <c r="E2" s="3">
+        <f>B2*C2</f>
+        <v/>
+      </c>
+      <c r="F2" s="4">
+        <f>E2-D2</f>
+        <v/>
+      </c>
+      <c r="G2" s="5">
+        <f>F2/E2</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bin 2</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D3" s="8">
-        <f>B3^2</f>
-        <v/>
-      </c>
-      <c r="E3" s="9">
-        <f>D3*C3</f>
-        <v/>
-      </c>
-      <c r="F3" s="10">
-        <f>ROUND(E3*$H$1,0)</f>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="D3" t="n">
+        <v>320</v>
+      </c>
+      <c r="E3" s="3">
+        <f>B3*C3</f>
+        <v/>
+      </c>
+      <c r="F3" s="4">
+        <f>E3-D3</f>
+        <v/>
+      </c>
+      <c r="G3" s="5">
+        <f>F3/E3</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bin 3</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="8">
-        <f>B4^2</f>
-        <v/>
-      </c>
-      <c r="E4" s="9">
-        <f>D4*C4</f>
-        <v/>
-      </c>
-      <c r="F4" s="10">
-        <f>ROUND(E4*$H$1,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Bin 4</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D5" s="8">
-        <f>B5^2</f>
-        <v/>
-      </c>
-      <c r="E5" s="9">
-        <f>D5*C5</f>
-        <v/>
-      </c>
-      <c r="F5" s="10">
-        <f>ROUND(E5*$H$1,0)</f>
+          <t>Barley</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>68</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>285</v>
+      </c>
+      <c r="E4" s="3">
+        <f>B4*C4</f>
+        <v/>
+      </c>
+      <c r="F4" s="4">
+        <f>E4-D4</f>
+        <v/>
+      </c>
+      <c r="G4" s="5">
+        <f>F4/E4</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E6" s="9">
-        <f>SUM(E2:E5)</f>
-        <v/>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Legend: colours mark question parts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11">
-        <f>4*3^2 gives</f>
-        <v/>
-      </c>
-      <c r="B8" s="11">
-        <f>4*3^2</f>
-        <v/>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11">
-        <f>(4*3)^2 gives</f>
-        <v/>
-      </c>
-      <c r="B9" s="11">
-        <f>(4*3)^2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>The two cells return 36 and 144. Exponents are evaluated before multiplication, so =4*3^2 squares the 3 and then multiplies by 4; the brackets in =(4*3)^2 force the multiplication first, and 12 squared is 144.</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>They doubled the side length instead of squaring it -- 11.25*2 is 22.5 m, a distance, not an area. Squaring gives 126.56 m².</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="n"/>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-      <c r="H15" s="14" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>Part (b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Part (c)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Part (d)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>Part (e)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A14:H15"/>
-    <mergeCell ref="A11:H12"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/practice/answers/s1_q21.xlsx
+++ b/practice/answers/s1_q21.xlsx
@@ -1,57 +1,122 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_884D9827905596AFE5126035491516BCBDF8F60D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A7F7C00-E1AE-46F8-979F-0EC141F80F7E}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Answer" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>Crop</t>
+  </si>
+  <si>
+    <t>Yield (bu/ac)</t>
+  </si>
+  <si>
+    <t>Price ($/bu)</t>
+  </si>
+  <si>
+    <t>Cost ($/ac)</t>
+  </si>
+  <si>
+    <t>Revenue ($/ac) (a)</t>
+  </si>
+  <si>
+    <t>Profit ($/ac) (b)</t>
+  </si>
+  <si>
+    <t>Margin (c)</t>
+  </si>
+  <si>
+    <t>Canola</t>
+  </si>
+  <si>
+    <t>Wheat</t>
+  </si>
+  <si>
+    <t>Barley</t>
+  </si>
+  <si>
+    <t>Legend: colours mark question parts</t>
+  </si>
+  <si>
+    <t>Part (a)</t>
+  </si>
+  <si>
+    <t>Part (b)</t>
+  </si>
+  <si>
+    <t>Part (c)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,88 +133,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -437,170 +443,137 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Crop</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Yield (bu/ac)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Price ($/bu)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Cost ($/ac)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Revenue ($/ac) (a)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Profit ($/ac) (b)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Margin (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Canola</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
         <v>42</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="2">
         <v>14.2</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>415</v>
       </c>
       <c r="E2" s="3">
         <f>B2*C2</f>
-        <v/>
+        <v>596.4</v>
       </c>
       <c r="F2" s="4">
         <f>E2-D2</f>
-        <v/>
+        <v>181.39999999999998</v>
       </c>
       <c r="G2" s="5">
         <f>F2/E2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Wheat</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+        <v>0.30415828303152243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
         <v>55</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="2">
         <v>8.35</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>320</v>
       </c>
       <c r="E3" s="3">
         <f>B3*C3</f>
-        <v/>
+        <v>459.25</v>
       </c>
       <c r="F3" s="4">
         <f>E3-D3</f>
-        <v/>
+        <v>139.25</v>
       </c>
       <c r="G3" s="5">
         <f>F3/E3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Barley</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+        <v>0.30321175830157865</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
         <v>68</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="2">
         <v>5.6</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>285</v>
       </c>
       <c r="E4" s="3">
         <f>B4*C4</f>
-        <v/>
+        <v>380.79999999999995</v>
       </c>
       <c r="F4" s="4">
         <f>E4-D4</f>
-        <v/>
+        <v>95.799999999999955</v>
       </c>
       <c r="G4" s="5">
         <f>F4/E4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Legend: colours mark question parts</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Part (b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Part (c)</t>
-        </is>
+        <v>0.25157563025210072</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
